--- a/Philadelphus.Presentation.Wpf.UI/Icons/Авторы.xlsx
+++ b/Philadelphus.Presentation.Wpf.UI/Icons/Авторы.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MelSV_Projects\Philadelphus.General\Philadelphus.Presentation.Wpf.UI\Icons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0157541C-87DF-4DAE-88CD-16DC6C059257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75290EFF-86CD-4AB5-9009-3C1605022B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-10200" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="105">
   <si>
     <t>Сайт</t>
   </si>
@@ -178,6 +178,171 @@
   </si>
   <si>
     <t>&lt;a href="https://www.flaticon.com/free-icons/list" title="list icons"&gt;List icons created by Chanut - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>broom.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/clear" title="clear icons"&gt;Clear icons created by LAFS - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/broom_9742093?term=clear&amp;page=1&amp;position=2&amp;origin=search&amp;related_id=9742093</t>
+  </si>
+  <si>
+    <t>broom_64.png</t>
+  </si>
+  <si>
+    <t>warning.png</t>
+  </si>
+  <si>
+    <t>warning_64.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/warning" title="warning icons"&gt;Warning icons created by Andrean Prabowo - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/warning_3756712?term=warning&amp;page=1&amp;position=4&amp;origin=search&amp;related_id=3756712</t>
+  </si>
+  <si>
+    <t>error-sign.png</t>
+  </si>
+  <si>
+    <t>error_64_1.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/error-sign" title="error sign icons"&gt;Error sign icons created by kawalanicon - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/error-sign_18532097</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/close_7268005</t>
+  </si>
+  <si>
+    <t>error_64_2.png</t>
+  </si>
+  <si>
+    <t>error_64_3.png</t>
+  </si>
+  <si>
+    <t>error_64_4.png</t>
+  </si>
+  <si>
+    <t>error_64_5.png</t>
+  </si>
+  <si>
+    <t>close.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/forbidden" title="forbidden icons"&gt;Forbidden icons created by Muhammad_Usman - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/cross_5629342</t>
+  </si>
+  <si>
+    <t>cross.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/cancel" title="cancel icons"&gt;Cancel icons created by Tama Icons. - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/error_6304695</t>
+  </si>
+  <si>
+    <t>error.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/close" title="close icons"&gt;Close icons created by Good Ware - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/error_8911729</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/shield" title="shield icons"&gt;Shield icons created by zero_wing - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/information_2460889</t>
+  </si>
+  <si>
+    <t>information.png</t>
+  </si>
+  <si>
+    <t>info_64_1.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/information" title="information icons"&gt;Information icons created by Aldo Cervantes - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/information_13077353</t>
+  </si>
+  <si>
+    <t>info_64_3.png</t>
+  </si>
+  <si>
+    <t>info_64_2.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/info" title="info icons"&gt;Info icons created by -Artist - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/info_7854848</t>
+  </si>
+  <si>
+    <t>info.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/info" title="info icons"&gt;Info icons created by Icon Hubs - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>soft_delete_64_1.png</t>
+  </si>
+  <si>
+    <t>soft_delete_64_2.png</t>
+  </si>
+  <si>
+    <t>hard_delete_64_1.png</t>
+  </si>
+  <si>
+    <t>hard_delete_64_2.png</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/delete_2907762</t>
+  </si>
+  <si>
+    <t>delete.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/delete" title="delete icons"&gt;Delete icons created by feen - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/delete_3132919</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/delete_14360493</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/recycle-bin" title="recycle bin icons"&gt;Recycle bin icons created by hqrloveq - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/trash_6460112</t>
+  </si>
+  <si>
+    <t>trash.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/delete" title="delete icons"&gt;Delete icons created by Arkinasi - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/fire-alarm_9509814</t>
+  </si>
+  <si>
+    <t>alarm_64.png</t>
+  </si>
+  <si>
+    <t>fire-alarm.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/fire-alarm" title="fire alarm icons"&gt;Fire alarm icons created by Muhammad_Usman - Flaticon&lt;/a&gt;</t>
   </si>
 </sst>
 </file>
@@ -528,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -742,6 +907,261 @@
         <v>46</v>
       </c>
     </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>

--- a/Philadelphus.Presentation.Wpf.UI/Icons/Авторы.xlsx
+++ b/Philadelphus.Presentation.Wpf.UI/Icons/Авторы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MelSV_Projects\Philadelphus.General\Philadelphus.Presentation.Wpf.UI\Icons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75290EFF-86CD-4AB5-9009-3C1605022B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD01880E-791B-4CCD-A813-F6CA4ECC08BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-10200" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Philadelphus.Presentation.Wpf.UI/Icons/Авторы.xlsx
+++ b/Philadelphus.Presentation.Wpf.UI/Icons/Авторы.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MelSV_Projects\Philadelphus.General\Philadelphus.Presentation.Wpf.UI\Icons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0157541C-87DF-4DAE-88CD-16DC6C059257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD01880E-791B-4CCD-A813-F6CA4ECC08BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-10200" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="105">
   <si>
     <t>Сайт</t>
   </si>
@@ -178,6 +178,171 @@
   </si>
   <si>
     <t>&lt;a href="https://www.flaticon.com/free-icons/list" title="list icons"&gt;List icons created by Chanut - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>broom.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/clear" title="clear icons"&gt;Clear icons created by LAFS - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/broom_9742093?term=clear&amp;page=1&amp;position=2&amp;origin=search&amp;related_id=9742093</t>
+  </si>
+  <si>
+    <t>broom_64.png</t>
+  </si>
+  <si>
+    <t>warning.png</t>
+  </si>
+  <si>
+    <t>warning_64.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/warning" title="warning icons"&gt;Warning icons created by Andrean Prabowo - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/warning_3756712?term=warning&amp;page=1&amp;position=4&amp;origin=search&amp;related_id=3756712</t>
+  </si>
+  <si>
+    <t>error-sign.png</t>
+  </si>
+  <si>
+    <t>error_64_1.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/error-sign" title="error sign icons"&gt;Error sign icons created by kawalanicon - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/error-sign_18532097</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/close_7268005</t>
+  </si>
+  <si>
+    <t>error_64_2.png</t>
+  </si>
+  <si>
+    <t>error_64_3.png</t>
+  </si>
+  <si>
+    <t>error_64_4.png</t>
+  </si>
+  <si>
+    <t>error_64_5.png</t>
+  </si>
+  <si>
+    <t>close.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/forbidden" title="forbidden icons"&gt;Forbidden icons created by Muhammad_Usman - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/cross_5629342</t>
+  </si>
+  <si>
+    <t>cross.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/cancel" title="cancel icons"&gt;Cancel icons created by Tama Icons. - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/error_6304695</t>
+  </si>
+  <si>
+    <t>error.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/close" title="close icons"&gt;Close icons created by Good Ware - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/error_8911729</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/shield" title="shield icons"&gt;Shield icons created by zero_wing - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/information_2460889</t>
+  </si>
+  <si>
+    <t>information.png</t>
+  </si>
+  <si>
+    <t>info_64_1.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/information" title="information icons"&gt;Information icons created by Aldo Cervantes - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/information_13077353</t>
+  </si>
+  <si>
+    <t>info_64_3.png</t>
+  </si>
+  <si>
+    <t>info_64_2.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/info" title="info icons"&gt;Info icons created by -Artist - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/info_7854848</t>
+  </si>
+  <si>
+    <t>info.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/info" title="info icons"&gt;Info icons created by Icon Hubs - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>soft_delete_64_1.png</t>
+  </si>
+  <si>
+    <t>soft_delete_64_2.png</t>
+  </si>
+  <si>
+    <t>hard_delete_64_1.png</t>
+  </si>
+  <si>
+    <t>hard_delete_64_2.png</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/delete_2907762</t>
+  </si>
+  <si>
+    <t>delete.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/delete" title="delete icons"&gt;Delete icons created by feen - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/delete_3132919</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/delete_14360493</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/recycle-bin" title="recycle bin icons"&gt;Recycle bin icons created by hqrloveq - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/trash_6460112</t>
+  </si>
+  <si>
+    <t>trash.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/delete" title="delete icons"&gt;Delete icons created by Arkinasi - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/fire-alarm_9509814</t>
+  </si>
+  <si>
+    <t>alarm_64.png</t>
+  </si>
+  <si>
+    <t>fire-alarm.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/fire-alarm" title="fire alarm icons"&gt;Fire alarm icons created by Muhammad_Usman - Flaticon&lt;/a&gt;</t>
   </si>
 </sst>
 </file>
@@ -528,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -742,6 +907,261 @@
         <v>46</v>
       </c>
     </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>

--- a/Philadelphus.Presentation.Wpf.UI/Icons/Авторы.xlsx
+++ b/Philadelphus.Presentation.Wpf.UI/Icons/Авторы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MelSV_Projects\Philadelphus.General\Philadelphus.Presentation.Wpf.UI\Icons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD01880E-791B-4CCD-A813-F6CA4ECC08BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EF1839-1870-4E73-A392-9CEB5023032D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-10200" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="175">
   <si>
     <t>Сайт</t>
   </si>
@@ -343,6 +343,216 @@
   </si>
   <si>
     <t>&lt;a href="https://www.flaticon.com/free-icons/fire-alarm" title="fire alarm icons"&gt;Fire alarm icons created by Muhammad_Usman - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>check-box.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/check-box" title="check box icons"&gt;Check box icons created by Tama Icons. - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/check-box_5629260</t>
+  </si>
+  <si>
+    <t>ok_64_1.png</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/check_12259192</t>
+  </si>
+  <si>
+    <t>ok_64_2.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/checked" title="checked icons"&gt;Checked icons created by rukanicon - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>check.png</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/decision_16921443</t>
+  </si>
+  <si>
+    <t>tree_64_1.png</t>
+  </si>
+  <si>
+    <t>decision.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/decision" title="decision icons"&gt;Decision icons created by kornkun - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/root_3127876</t>
+  </si>
+  <si>
+    <t>root.png</t>
+  </si>
+  <si>
+    <t>tree_64_2.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/root" title="root icons"&gt;Root icons created by IYIKON - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/tree-of-life_11015275</t>
+  </si>
+  <si>
+    <t>tree-of-life.png</t>
+  </si>
+  <si>
+    <t>tree_64_3.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/tree-of-life" title="tree of life icons"&gt;Tree of life icons created by Freepik - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/tree-of-life_11015259</t>
+  </si>
+  <si>
+    <t>tree_64_4.png</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/phylogenetic_8682093</t>
+  </si>
+  <si>
+    <t>phylogenetic.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/phylogenetic" title="phylogenetic icons"&gt;Phylogenetic icons created by Muhammad Waqas Khan - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>tree_64_5.png</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/root_8053617</t>
+  </si>
+  <si>
+    <t>tree_64_6.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/root" title="root icons"&gt;Root icons created by JV Design - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/plant_1186624</t>
+  </si>
+  <si>
+    <t>plant.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/soil" title="soil icons"&gt;Soil icons created by Freepik - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>tree_64_7.png</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/root_3239230</t>
+  </si>
+  <si>
+    <t>root_64_1.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/root" title="root icons"&gt;Root icons created by dDara - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>tree_64_8.png</t>
+  </si>
+  <si>
+    <t>root_64_2.png</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/root_18668071</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/tuber" title="tuber icons"&gt;Tuber icons created by Sympnoiaicon - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/branch_3693484</t>
+  </si>
+  <si>
+    <t>node_64_1.png</t>
+  </si>
+  <si>
+    <t>branch.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/branch" title="branch icons"&gt;Branch icons created by kornkun - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>twig.png</t>
+  </si>
+  <si>
+    <t>node_64_2.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/tree-branch" title="tree branch icons"&gt;Tree branch icons created by POD Gladiator - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/twig_17837126</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/flower_5240766</t>
+  </si>
+  <si>
+    <t>flower.png</t>
+  </si>
+  <si>
+    <t>node_64_3.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/branch" title="branch icons"&gt;Branch icons created by Freepik - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/leaf_748049</t>
+  </si>
+  <si>
+    <t>leave_64_1.png</t>
+  </si>
+  <si>
+    <t>leaf.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/leave" title="leave icons"&gt;Leave icons created by Freepik - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/leaves_18987039</t>
+  </si>
+  <si>
+    <t>leaves.png</t>
+  </si>
+  <si>
+    <t>leave_64_2.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/leave" title="leave icons"&gt;Leave icons created by Mike Zuidgeest - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/leave_2345715</t>
+  </si>
+  <si>
+    <t>leave.png</t>
+  </si>
+  <si>
+    <t>leave_64_3.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/botany" title="botany icons"&gt;Botany icons created by kurdanfell - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>leave_info_64.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/plant" title="plant icons"&gt;Plant icons created by Freepik - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/leave_1186607</t>
+  </si>
+  <si>
+    <t>search_64_1.png</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.flaticon.com/free-icons/search" title="search icons"&gt;Search icons created by Kiranshastry - Flaticon&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>https://www.flaticon.com/free-icon/search_711319</t>
   </si>
 </sst>
 </file>
@@ -693,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -926,240 +1136,580 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -1169,8 +1719,9 @@
     <hyperlink ref="E8" r:id="rId2" xr:uid="{801744F8-AA42-4DBA-B71D-1CE65AD75811}"/>
     <hyperlink ref="E9" r:id="rId3" xr:uid="{EE2FB710-D0B1-4C8A-A16B-340DF3C02C77}"/>
     <hyperlink ref="E10" r:id="rId4" xr:uid="{1D2B95C9-C435-4B8C-974A-21672A5CE58B}"/>
+    <hyperlink ref="E47" r:id="rId5" xr:uid="{434D9141-B269-48AB-AA89-C3D13E391DDF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>